--- a/artfynd/A 41553-2025 artfynd.xlsx
+++ b/artfynd/A 41553-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112079324</v>
+        <v>112314330</v>
       </c>
       <c r="B2" t="n">
-        <v>89847</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1964</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Honungsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Flavidoporia mellita</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Niemelä &amp; Penttillä) Audet</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475641</v>
+        <v>475622</v>
       </c>
       <c r="R2" t="n">
-        <v>6777743</v>
+        <v>6777762</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,17 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På en klen asplåga.</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,45 +761,25 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112314284</v>
+        <v>112079324</v>
       </c>
       <c r="B3" t="n">
-        <v>89853</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92201</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -826,12 +796,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Flavidoporia mellita</t>
+          <t>Fomitopsis mellita</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Niemelä &amp; Penttillä) Audet</t>
+          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -844,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475632</v>
+        <v>475641</v>
       </c>
       <c r="R3" t="n">
-        <v>6777743</v>
+        <v>6777744</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,17 +844,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Känd lokal, hittad av Anton Björk, på asplåga cirka 15 cm i diameter</t>
+          <t>På en klen asplåga.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,30 +867,40 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119331190</v>
+        <v>112314284</v>
       </c>
       <c r="B4" t="n">
-        <v>90824</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -937,19 +917,15 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Flavidoporia mellita</t>
+          <t>Fomitopsis mellita</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Niemelä &amp; Penttillä) Audet</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -989,12 +965,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Känd lokal, hittad av Anton Björk, på asplåga cirka 15 cm i diameter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,12 +1006,7 @@
         <v>119372264</v>
       </c>
       <c r="B5" t="n">
-        <v>90824</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92201</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,12 +1023,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Flavidoporia mellita</t>
+          <t>Fomitopsis mellita</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Niemelä &amp; Penttillä) Audet</t>
+          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1131,6 +1107,113 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128481218</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91893</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4660</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rävticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Inocutis rheades</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sliparbacken, Sliparbacken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>475391</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6777695</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41553-2025 artfynd.xlsx
+++ b/artfynd/A 41553-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112314330</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112079324</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,6 +1015,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112314284</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1107,6 +1127,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119372264</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1214,8 +1239,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128481218</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>